--- a/artfynd/A 62817-2021 artfynd.xlsx
+++ b/artfynd/A 62817-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124145723</v>
+        <v>124145725</v>
       </c>
       <c r="B2" t="n">
         <v>56700</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549438</v>
+        <v>549514</v>
       </c>
       <c r="R2" t="n">
-        <v>6324559</v>
+        <v>6324646</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124145725</v>
+        <v>124145723</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549514</v>
+        <v>549438</v>
       </c>
       <c r="R3" t="n">
-        <v>6324646</v>
+        <v>6324559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 62817-2021 artfynd.xlsx
+++ b/artfynd/A 62817-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124145725</v>
+        <v>124145723</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549514</v>
+        <v>549438</v>
       </c>
       <c r="R2" t="n">
-        <v>6324646</v>
+        <v>6324559</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124145723</v>
+        <v>124145725</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549438</v>
+        <v>549514</v>
       </c>
       <c r="R3" t="n">
-        <v>6324559</v>
+        <v>6324646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 62817-2021 artfynd.xlsx
+++ b/artfynd/A 62817-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124145723</v>
+        <v>124145725</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549438</v>
+        <v>549514</v>
       </c>
       <c r="R2" t="n">
-        <v>6324559</v>
+        <v>6324646</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124145725</v>
+        <v>124145723</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549514</v>
+        <v>549438</v>
       </c>
       <c r="R3" t="n">
-        <v>6324646</v>
+        <v>6324559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 62817-2021 artfynd.xlsx
+++ b/artfynd/A 62817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>124145723</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,12 +809,7 @@
         <v>124145725</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,15 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124570320</v>
+        <v>124570276</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549512</v>
+        <v>549402</v>
       </c>
       <c r="R4" t="n">
-        <v>6324582</v>
+        <v>6324525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1056,12 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Jag tror inte att det var samma som en timme innan, den här var beige-brun i färgen, den andra hade mycket mer rödbrun färg. Men jag kan inte säga säkert.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1085,6 +1065,890 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124570320</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549512</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6324582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Jag tror inte att det var samma som en timme innan, den här var beige-brun i färgen, den andra hade mycket mer rödbrun färg. Men jag kan inte säga säkert.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125553858</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6324572</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122894429</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hygget Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549410</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6324619</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert, Mats Johansson, Urban Rundström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97956327</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>O om Flatehult, Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549517</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6324606</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tupp, flög mot sydost JSN0179 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122512564</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dahlströmsvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549542</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6324601</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>wurb2024 KA-02 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125030401</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dahlströmsvägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549504</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6324667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126155562</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogavägen, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549402</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6324525</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62817-2021 artfynd.xlsx
+++ b/artfynd/A 62817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124145723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124145725</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124570276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1201,6 +1221,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124570320</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1332,6 +1357,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125553858</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1459,6 +1489,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122894429</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97956327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1694,6 +1734,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122512564</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1821,6 +1866,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125030401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1949,8 +1999,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126155562</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>